--- a/artfynd/A 43822-2023 artfynd.xlsx
+++ b/artfynd/A 43822-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43822-2023 artfynd.xlsx
+++ b/artfynd/A 43822-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>74945865</v>
+        <v>112491350</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,40 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>SW Strandåsmyren, Vrm</t>
+          <t>Älggropsröset, Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>356552.7924764203</v>
+        <v>356638</v>
       </c>
       <c r="R2" t="n">
-        <v>6743378.883647846</v>
+        <v>6743421</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,27 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperier på gammeltall</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,33 +757,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>74945847</v>
+        <v>112491369</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +787,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>SW Strandåsmyren, Vrm</t>
+          <t>Älggropsröset, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>356509.9610517538</v>
+        <v>356588</v>
       </c>
       <c r="R3" t="n">
-        <v>6743043.910043963</v>
+        <v>6743347</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,27 +844,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Garnlavsdraperier på gammeltall</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,33 +863,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>74945867</v>
+        <v>112491388</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +893,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>SW Strandåsmyren, Vrm</t>
+          <t>Älggropsröset, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>356567.181805349</v>
+        <v>356590</v>
       </c>
       <c r="R4" t="n">
-        <v>6743408.112830303</v>
+        <v>6743003</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,27 +950,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Garnlavsdraperier på gammeltall</t>
+          <t>2023-10-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,37 +964,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Per Gustafsson</t>
+          <t>Jonas Göransson, August Oljeqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>74945859</v>
+        <v>74945847</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1066,10 +1018,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>356455.1272816613</v>
+        <v>356510</v>
       </c>
       <c r="R5" t="n">
-        <v>6743287.033571675</v>
+        <v>6743044</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1099,19 +1051,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1143,37 +1085,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>74945835</v>
+        <v>74945850</v>
       </c>
       <c r="B6" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1120,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>356515.8841641105</v>
+        <v>356445</v>
       </c>
       <c r="R6" t="n">
-        <v>6743045.138037706</v>
+        <v>6743082</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1216,19 +1153,14 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperier på gammeltall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,19 +1187,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>74945857</v>
+        <v>74945852</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1295,10 +1222,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>356453.1707879578</v>
+        <v>356412</v>
       </c>
       <c r="R7" t="n">
-        <v>6743274.895661449</v>
+        <v>6743211</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1328,19 +1255,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1372,37 +1289,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>74945841</v>
+        <v>74945854</v>
       </c>
       <c r="B8" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1412,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>356515.8841641105</v>
+        <v>356415</v>
       </c>
       <c r="R8" t="n">
-        <v>6743045.138037706</v>
+        <v>6743226</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1445,19 +1357,14 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlavsdraperier på gammeltall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1484,19 +1391,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>74945850</v>
+        <v>74945857</v>
       </c>
       <c r="B9" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1524,10 +1426,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>356444.9316677378</v>
+        <v>356453</v>
       </c>
       <c r="R9" t="n">
-        <v>6743082.199295346</v>
+        <v>6743275</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1557,19 +1459,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
@@ -1601,19 +1493,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>74945852</v>
+        <v>74945859</v>
       </c>
       <c r="B10" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1641,10 +1528,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>356411.9368628464</v>
+        <v>356455</v>
       </c>
       <c r="R10" t="n">
-        <v>6743211.07251817</v>
+        <v>6743287</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1674,19 +1561,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1721,16 +1598,11 @@
         <v>74945863</v>
       </c>
       <c r="B11" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1758,10 +1630,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>356541.2187339678</v>
+        <v>356541</v>
       </c>
       <c r="R11" t="n">
-        <v>6743358.825495692</v>
+        <v>6743359</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1791,19 +1663,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1835,19 +1697,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>74945854</v>
+        <v>74945865</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1875,10 +1732,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>356414.9886085341</v>
+        <v>356553</v>
       </c>
       <c r="R12" t="n">
-        <v>6743226.098610193</v>
+        <v>6743379</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1908,19 +1765,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
@@ -1952,69 +1799,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>74828367</v>
+        <v>74945867</v>
       </c>
       <c r="B13" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>SV Strandåsmyren, Vrm</t>
+          <t>SW Strandåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>356740.4320604312</v>
+        <v>356567</v>
       </c>
       <c r="R13" t="n">
-        <v>6743103.069505866</v>
+        <v>6743408</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2041,24 +1867,14 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>14:05</t>
-        </is>
-      </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>I en liten nyckelbiotop sydväst om Strandåsmyren.</t>
+          <t>Garnlavsdraperier på gammeltall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,23 +1897,14 @@
           <t>Per Gustafsson</t>
         </is>
       </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>Jobbkryss</t>
-        </is>
-      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>112491369</v>
+        <v>74945841</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2105,40 +1912,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Älggropsröset, Vrm</t>
+          <t>SW Strandåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>356588</v>
+        <v>356516</v>
       </c>
       <c r="R14" t="n">
-        <v>6743347</v>
+        <v>6743045</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2162,17 +1966,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2018-11-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På björk</t>
+          <t>2018-11-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2181,34 +1980,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>112491388</v>
+        <v>74828367</v>
       </c>
       <c r="B15" t="n">
-        <v>90945</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2216,40 +2009,53 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5966</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Älggropsröset, Vrm</t>
+          <t>SV Strandåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>356591</v>
+        <v>356740</v>
       </c>
       <c r="R15" t="n">
-        <v>6743003</v>
+        <v>6743103</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2273,12 +2079,27 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>I en liten nyckelbiotop sydväst om Strandåsmyren.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,75 +2108,74 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Jobbkryss</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>112491350</v>
+        <v>74945818</v>
       </c>
       <c r="B16" t="n">
-        <v>81483</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Älggropsröset, Vrm</t>
+          <t>SW Strandåsmyren, Vrm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>356637</v>
+        <v>356438</v>
       </c>
       <c r="R16" t="n">
-        <v>6743421</v>
+        <v>6743130</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2379,12 +2199,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2018-11-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-10-02</t>
+          <t>2018-11-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2393,22 +2213,122 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Jonas Göransson</t>
+          <t>Per Gustafsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Jonas Göransson, August Oljeqvist</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Jobbkryss</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>74945835</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SW Strandåsmyren, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>356516</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6743045</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Södra Finnskoga</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Per Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43822-2023 artfynd.xlsx
+++ b/artfynd/A 43822-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -980,6 +995,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112491388</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1082,6 +1102,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945847</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1184,6 +1209,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945850</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945852</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1388,6 +1423,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945854</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1490,6 +1530,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945857</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1592,6 +1637,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945859</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1694,6 +1744,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945863</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1796,6 +1851,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945865</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +1958,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945867</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945841</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2127,6 +2197,11 @@
           <t>Jobbkryss</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74828367</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2232,6 +2307,11 @@
           <t>Jobbkryss</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945818</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2329,8 +2409,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74945835</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>